--- a/data/trans_orig/P2C_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P2C_R-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>54809</t>
+          <t>54601</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>66773</t>
+          <t>67118</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>68,12%</t>
+          <t>67,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>82,99%</t>
+          <t>83,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>44653</t>
+          <t>44877</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>56634</t>
+          <t>57323</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>62,33%</t>
+          <t>62,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>79,06%</t>
+          <t>80,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>103543</t>
+          <t>102923</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>121266</t>
+          <t>121429</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>68,08%</t>
+          <t>67,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>79,73%</t>
+          <t>79,84%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13682</t>
+          <t>13337</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25646</t>
+          <t>25854</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>32,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15003</t>
+          <t>14314</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>26984</t>
+          <t>26760</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>37,67%</t>
+          <t>37,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>30826</t>
+          <t>30663</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>48549</t>
+          <t>49169</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>32,33%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>43510</t>
+          <t>43965</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>55718</t>
+          <t>55842</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>63,34%</t>
+          <t>64,01%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>81,12%</t>
+          <t>81,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>45553</t>
+          <t>45408</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>56753</t>
+          <t>56856</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>67,5%</t>
+          <t>67,29%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>84,1%</t>
+          <t>84,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>92770</t>
+          <t>93711</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>109334</t>
+          <t>110635</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>68,13%</t>
+          <t>68,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>80,29%</t>
+          <t>81,25%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>12969</t>
+          <t>12845</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>25177</t>
+          <t>24722</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>36,66%</t>
+          <t>35,99%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>10732</t>
+          <t>10629</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>21932</t>
+          <t>22077</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>32,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>26838</t>
+          <t>25537</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>43402</t>
+          <t>42461</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>31,18%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>29306</t>
+          <t>28831</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>41435</t>
+          <t>41149</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>50,31%</t>
+          <t>49,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>71,14%</t>
+          <t>70,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>49215</t>
+          <t>49232</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>62672</t>
+          <t>62908</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>58,63%</t>
+          <t>58,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>74,66%</t>
+          <t>74,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>82074</t>
+          <t>81837</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>100709</t>
+          <t>100286</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>57,72%</t>
+          <t>57,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>70,83%</t>
+          <t>70,53%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16810</t>
+          <t>17096</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>28939</t>
+          <t>29414</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>49,69%</t>
+          <t>50,5%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21272</t>
+          <t>21036</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>34729</t>
+          <t>34712</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>41,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>41480</t>
+          <t>41903</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>60115</t>
+          <t>60352</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,28%</t>
+          <t>42,45%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>90120</t>
+          <t>90459</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>109603</t>
+          <t>109346</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>59,57%</t>
+          <t>59,79%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>72,44%</t>
+          <t>72,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>92280</t>
+          <t>92702</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>110415</t>
+          <t>111195</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>62,12%</t>
+          <t>62,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>74,32%</t>
+          <t>74,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>187259</t>
+          <t>188656</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>213573</t>
+          <t>214226</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>62,45%</t>
+          <t>62,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>71,22%</t>
+          <t>71,44%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>41693</t>
+          <t>41950</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>61176</t>
+          <t>60837</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>40,43%</t>
+          <t>40,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>38147</t>
+          <t>37367</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>56282</t>
+          <t>55860</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>37,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>86285</t>
+          <t>85632</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>112599</t>
+          <t>111202</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>37,55%</t>
+          <t>37,08%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>43652</t>
+          <t>43083</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>55855</t>
+          <t>55152</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>63,15%</t>
+          <t>62,33%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>80,81%</t>
+          <t>79,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>50874</t>
+          <t>51579</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>64635</t>
+          <t>64302</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>60,18%</t>
+          <t>61,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>76,46%</t>
+          <t>76,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>99041</t>
+          <t>98322</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>116187</t>
+          <t>116374</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>64,46%</t>
+          <t>63,99%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>75,62%</t>
+          <t>75,74%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13268</t>
+          <t>13971</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25471</t>
+          <t>26040</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>37,67%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19895</t>
+          <t>20228</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>33656</t>
+          <t>32951</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>39,82%</t>
+          <t>38,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>37465</t>
+          <t>37278</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>54611</t>
+          <t>55330</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>36,01%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>46784</t>
+          <t>46136</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>58797</t>
+          <t>58866</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>62,49%</t>
+          <t>61,62%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>78,53%</t>
+          <t>78,62%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>37188</t>
+          <t>37407</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>50721</t>
+          <t>50634</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>51,37%</t>
+          <t>51,67%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>70,06%</t>
+          <t>69,94%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>87479</t>
+          <t>87794</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>106080</t>
+          <t>106060</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>59,4%</t>
+          <t>59,62%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>72,03%</t>
+          <t>72,02%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>16073</t>
+          <t>16004</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>28086</t>
+          <t>28734</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>38,38%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>21671</t>
+          <t>21758</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>35204</t>
+          <t>34985</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>48,63%</t>
+          <t>48,33%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>41182</t>
+          <t>41202</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>59783</t>
+          <t>59468</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>40,6%</t>
+          <t>40,38%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>332913</t>
+          <t>331600</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>366154</t>
+          <t>365980</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>66,23%</t>
+          <t>65,97%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>72,84%</t>
+          <t>72,81%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>346609</t>
+          <t>346730</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>381488</t>
+          <t>380608</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>65,58%</t>
+          <t>65,6%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>72,18%</t>
+          <t>72,01%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>689159</t>
+          <t>689566</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>737998</t>
+          <t>737493</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>66,83%</t>
+          <t>66,87%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>71,57%</t>
+          <t>71,52%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>136521</t>
+          <t>136695</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>169762</t>
+          <t>171075</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>147061</t>
+          <t>147941</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>181940</t>
+          <t>181819</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>27,99%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>34,42%</t>
+          <t>34,4%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>293227</t>
+          <t>293732</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>342066</t>
+          <t>341659</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>28,48%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>33,13%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>49078</t>
+          <t>48368</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>57266</t>
+          <t>57389</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>80,16%</t>
+          <t>79,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>59338</t>
+          <t>58982</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>67928</t>
+          <t>67927</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>80,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>111245</t>
+          <t>111751</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>123774</t>
+          <t>123628</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>83,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>91,83%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3955</t>
+          <t>3832</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12143</t>
+          <t>12853</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5482</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14072</t>
+          <t>14428</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3536,7 +3536,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10857</t>
+          <t>11003</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>23386</t>
+          <t>22880</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>16,99%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>57113</t>
+          <t>57777</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>64017</t>
+          <t>63983</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>88,37%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>63082</t>
+          <t>63044</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>67906</t>
+          <t>67898</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>123185</t>
+          <t>122920</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>130661</t>
+          <t>130798</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,68%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1362</t>
+          <t>1396</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8266</t>
+          <t>7602</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>628</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5444</t>
+          <t>5482</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3244</t>
+          <t>3107</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>10720</t>
+          <t>10985</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,2%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>54014</t>
+          <t>53809</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>62466</t>
+          <t>62540</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>81,2%</t>
+          <t>80,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>52056</t>
+          <t>51744</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>62134</t>
+          <t>62102</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>76,59%</t>
+          <t>76,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>91,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>109251</t>
+          <t>108634</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>122338</t>
+          <t>122051</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>81,24%</t>
+          <t>80,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>90,75%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4057</t>
+          <t>3983</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12509</t>
+          <t>12714</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5830</t>
+          <t>5862</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15908</t>
+          <t>16220</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>12149</t>
+          <t>12436</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>25236</t>
+          <t>25853</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>19,22%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>114835</t>
+          <t>114974</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>126801</t>
+          <t>126080</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>84,14%</t>
+          <t>84,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>131084</t>
+          <t>130402</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>145960</t>
+          <t>145808</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>81,23%</t>
+          <t>80,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>90,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>251362</t>
+          <t>250760</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>269790</t>
+          <t>269538</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>84,39%</t>
+          <t>84,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>90,58%</t>
+          <t>90,5%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>10400</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>21645</t>
+          <t>21506</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>15404</t>
+          <t>15556</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>30280</t>
+          <t>30962</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>28054</t>
+          <t>28306</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>46482</t>
+          <t>47084</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,81%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>78674</t>
+          <t>78587</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>88333</t>
+          <t>88476</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>84,19%</t>
+          <t>84,09%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>80488</t>
+          <t>80528</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>88732</t>
+          <t>88737</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>87,48%</t>
+          <t>87,52%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>163302</t>
+          <t>162864</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>175212</t>
+          <t>175430</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>88,05%</t>
+          <t>87,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,59%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5118</t>
+          <t>4975</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14777</t>
+          <t>14864</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3276</t>
+          <t>3271</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11520</t>
+          <t>11480</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>10247</t>
+          <t>10029</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>22157</t>
+          <t>22595</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>12,18%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>44546</t>
+          <t>44846</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>51830</t>
+          <t>51854</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>83,19%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>52244</t>
+          <t>52328</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>63694</t>
+          <t>63265</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>70,56%</t>
+          <t>70,68%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>85,45%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>99699</t>
+          <t>100481</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>113490</t>
+          <t>114364</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>77,92%</t>
+          <t>78,53%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>88,7%</t>
+          <t>89,38%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2081</t>
+          <t>2057</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9365</t>
+          <t>9065</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>10344</t>
+          <t>10773</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>21794</t>
+          <t>21710</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>14459</t>
+          <t>13585</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>28250</t>
+          <t>27468</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>21,47%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>417091</t>
+          <t>418324</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>439171</t>
+          <t>438557</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>87,71%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>459450</t>
+          <t>458125</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>483743</t>
+          <t>483747</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>85,51%</t>
+          <t>85,26%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>882899</t>
+          <t>884932</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>917690</t>
+          <t>916801</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>87,05%</t>
+          <t>87,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,39%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>37794</t>
+          <t>38408</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>59874</t>
+          <t>58641</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>53567</t>
+          <t>53563</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>77860</t>
+          <t>79185</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5594,7 +5594,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>96585</t>
+          <t>97474</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>131376</t>
+          <t>129343</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,75%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>42521</t>
+          <t>41927</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>54399</t>
+          <t>54556</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>65,59%</t>
+          <t>64,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>83,91%</t>
+          <t>84,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>58443</t>
+          <t>58717</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>69419</t>
+          <t>69771</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>74,68%</t>
+          <t>75,03%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>89,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>104873</t>
+          <t>104789</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>120471</t>
+          <t>121081</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>73,29%</t>
+          <t>73,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>84,2%</t>
+          <t>84,62%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10432</t>
+          <t>10275</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22310</t>
+          <t>22904</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,41%</t>
+          <t>35,33%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8835</t>
+          <t>8483</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19811</t>
+          <t>19537</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>22614</t>
+          <t>22004</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>38212</t>
+          <t>38296</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,76%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>53139</t>
+          <t>53535</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>66470</t>
+          <t>66574</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>64,56%</t>
+          <t>65,04%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>80,76%</t>
+          <t>80,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>62543</t>
+          <t>61301</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>75634</t>
+          <t>75661</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>67,2%</t>
+          <t>65,87%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>81,27%</t>
+          <t>81,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>119225</t>
+          <t>119866</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>139025</t>
+          <t>138715</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>67,98%</t>
+          <t>68,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>79,27%</t>
+          <t>79,09%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>15841</t>
+          <t>15737</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>29172</t>
+          <t>28776</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>34,96%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>17433</t>
+          <t>17406</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>30524</t>
+          <t>31766</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>32,8%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>36353</t>
+          <t>36663</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>56153</t>
+          <t>55512</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>31,65%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>28328</t>
+          <t>28100</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39015</t>
+          <t>39051</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>57,55%</t>
+          <t>57,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>79,26%</t>
+          <t>79,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>35487</t>
+          <t>36053</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>47558</t>
+          <t>48008</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>58,16%</t>
+          <t>59,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>77,95%</t>
+          <t>78,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>69057</t>
+          <t>68926</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>84570</t>
+          <t>84457</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>62,65%</t>
+          <t>62,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>76,72%</t>
+          <t>76,62%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10209</t>
+          <t>10173</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20896</t>
+          <t>21124</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>42,45%</t>
+          <t>42,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13453</t>
+          <t>13003</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>25524</t>
+          <t>24958</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>41,84%</t>
+          <t>40,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>25664</t>
+          <t>25777</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>41177</t>
+          <t>41308</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>37,35%</t>
+          <t>37,47%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>114531</t>
+          <t>114420</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>133550</t>
+          <t>132865</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>69,08%</t>
+          <t>69,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>80,55%</t>
+          <t>80,14%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>120904</t>
+          <t>120106</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>139706</t>
+          <t>139521</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>70,75%</t>
+          <t>70,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>81,76%</t>
+          <t>81,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>239494</t>
+          <t>240856</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>266994</t>
+          <t>267080</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>71,13%</t>
+          <t>71,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>79,3%</t>
+          <t>79,33%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>32247</t>
+          <t>32932</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>51266</t>
+          <t>51377</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>31177</t>
+          <t>31362</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>49979</t>
+          <t>50777</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>69686</t>
+          <t>69600</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>97186</t>
+          <t>95824</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>28,46%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>71150</t>
+          <t>71706</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>85157</t>
+          <t>85440</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>70,04%</t>
+          <t>70,59%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>83,83%</t>
+          <t>84,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>71168</t>
+          <t>70805</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>84632</t>
+          <t>83996</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>71,78%</t>
+          <t>71,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>85,36%</t>
+          <t>84,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>146066</t>
+          <t>146164</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>165810</t>
+          <t>165559</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>72,77%</t>
+          <t>72,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>82,6%</t>
+          <t>82,48%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16422</t>
+          <t>16139</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>30429</t>
+          <t>29873</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>14521</t>
+          <t>15157</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>27985</t>
+          <t>28348</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>34922</t>
+          <t>35173</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>54666</t>
+          <t>54568</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>27,18%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>29143</t>
+          <t>29754</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>41400</t>
+          <t>42246</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>48,3%</t>
+          <t>49,32%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>68,62%</t>
+          <t>70,02%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>39140</t>
+          <t>39460</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>51947</t>
+          <t>51763</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>57,71%</t>
+          <t>58,18%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>76,59%</t>
+          <t>76,32%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>71770</t>
+          <t>71333</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>90985</t>
+          <t>90081</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>56,0%</t>
+          <t>55,66%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>70,99%</t>
+          <t>70,29%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>18934</t>
+          <t>18088</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>31191</t>
+          <t>30580</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>51,7%</t>
+          <t>50,68%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>15878</t>
+          <t>16062</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>28685</t>
+          <t>28365</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>42,29%</t>
+          <t>41,82%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>37174</t>
+          <t>38078</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>56389</t>
+          <t>56826</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>44,0%</t>
+          <t>44,34%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>364897</t>
+          <t>366503</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>399986</t>
+          <t>399859</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>69,63%</t>
+          <t>69,93%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>76,32%</t>
+          <t>76,3%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>412928</t>
+          <t>413604</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>447509</t>
+          <t>448191</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>72,42%</t>
+          <t>72,54%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>78,48%</t>
+          <t>78,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>788357</t>
+          <t>791865</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>838201</t>
+          <t>840237</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>72,04%</t>
+          <t>72,36%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>76,6%</t>
+          <t>76,79%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>124090</t>
+          <t>124217</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>159179</t>
+          <t>157573</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>122683</t>
+          <t>122001</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>157264</t>
+          <t>156588</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>256067</t>
+          <t>254031</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>305911</t>
+          <t>302403</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>27,64%</t>
         </is>
       </c>
     </row>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18815</t>
+          <t>18600</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33331</t>
+          <t>32704</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>31,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>26881</t>
+          <t>26929</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>46881</t>
+          <t>46862</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>34,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>50919</t>
+          <t>50457</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>74371</t>
+          <t>73927</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>30,63%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>71131</t>
+          <t>71758</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>85647</t>
+          <t>85862</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>68,09%</t>
+          <t>68,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,99%</t>
+          <t>82,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>90027</t>
+          <t>90046</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>110027</t>
+          <t>109979</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>65,76%</t>
+          <t>65,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>80,37%</t>
+          <t>80,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>166999</t>
+          <t>167443</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>190451</t>
+          <t>190913</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>69,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>78,9%</t>
+          <t>79,1%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22491</t>
+          <t>22266</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>37778</t>
+          <t>37310</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>39,9%</t>
+          <t>39,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19825</t>
+          <t>20175</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>35110</t>
+          <t>35300</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>36,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>45082</t>
+          <t>46338</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>67639</t>
+          <t>68243</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>35,87%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>56903</t>
+          <t>57371</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>72190</t>
+          <t>72415</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>60,1%</t>
+          <t>60,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>76,25%</t>
+          <t>76,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>60463</t>
+          <t>60273</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>75748</t>
+          <t>75398</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>63,26%</t>
+          <t>63,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,26%</t>
+          <t>78,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>122615</t>
+          <t>122011</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>145172</t>
+          <t>143916</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>64,45%</t>
+          <t>64,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>76,3%</t>
+          <t>75,64%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11579</t>
+          <t>11797</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23599</t>
+          <t>23723</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>45,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14082</t>
+          <t>14032</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27063</t>
+          <t>27480</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,38%</t>
+          <t>43,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>29268</t>
+          <t>28813</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>47193</t>
+          <t>46389</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>40,78%</t>
+          <t>40,09%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>28262</t>
+          <t>28138</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>40282</t>
+          <t>40064</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>54,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>77,67%</t>
+          <t>77,25%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>36790</t>
+          <t>36373</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>49771</t>
+          <t>49821</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>57,62%</t>
+          <t>56,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>77,95%</t>
+          <t>78,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>68521</t>
+          <t>69325</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>86446</t>
+          <t>86901</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>59,22%</t>
+          <t>59,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>74,71%</t>
+          <t>75,1%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>35634</t>
+          <t>36986</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>70614</t>
+          <t>70023</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>51210</t>
+          <t>51107</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>76027</t>
+          <t>75546</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>34,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>89039</t>
+          <t>93667</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>136742</t>
+          <t>137269</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>31,4%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>148211</t>
+          <t>148802</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>183191</t>
+          <t>181839</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>67,73%</t>
+          <t>68,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,72%</t>
+          <t>83,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>142245</t>
+          <t>142726</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>167062</t>
+          <t>167165</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>65,17%</t>
+          <t>65,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,54%</t>
+          <t>76,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>300355</t>
+          <t>299828</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>348058</t>
+          <t>343430</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,72%</t>
+          <t>68,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,63%</t>
+          <t>78,57%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>31873</t>
+          <t>31965</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>49400</t>
+          <t>49131</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>41,36%</t>
+          <t>41,14%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>54396</t>
+          <t>53705</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>87969</t>
+          <t>88580</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>33,45%</t>
+          <t>33,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>54,1%</t>
+          <t>54,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>91818</t>
+          <t>90868</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>131331</t>
+          <t>130172</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>32,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>46,56%</t>
+          <t>46,15%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>70028</t>
+          <t>70297</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>87555</t>
+          <t>87463</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>58,64%</t>
+          <t>58,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>73,31%</t>
+          <t>73,24%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>74648</t>
+          <t>74037</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>108221</t>
+          <t>108912</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>45,9%</t>
+          <t>45,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>66,55%</t>
+          <t>66,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>150714</t>
+          <t>151873</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>190227</t>
+          <t>191177</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>53,44%</t>
+          <t>53,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>67,45%</t>
+          <t>67,78%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>20860</t>
+          <t>21036</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>35341</t>
+          <t>35417</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>51,3%</t>
+          <t>51,41%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>26810</t>
+          <t>27077</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>42711</t>
+          <t>43152</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>37,24%</t>
+          <t>37,61%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>59,32%</t>
+          <t>59,93%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>52314</t>
+          <t>51866</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>74261</t>
+          <t>73170</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>37,13%</t>
+          <t>36,81%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>52,71%</t>
+          <t>51,93%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>33554</t>
+          <t>33478</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>48035</t>
+          <t>47859</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>48,7%</t>
+          <t>48,59%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>69,72%</t>
+          <t>69,47%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>29292</t>
+          <t>28851</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>45193</t>
+          <t>44926</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>40,07%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>62,76%</t>
+          <t>62,39%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>66637</t>
+          <t>67728</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>88584</t>
+          <t>89032</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>47,29%</t>
+          <t>48,07%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>62,87%</t>
+          <t>63,19%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>168819</t>
+          <t>165817</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>218595</t>
+          <t>218657</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>25,19%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>33,22%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>222088</t>
+          <t>223745</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>277065</t>
+          <t>278367</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>29,86%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>36,98%</t>
+          <t>37,15%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>401709</t>
+          <t>403175</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>479076</t>
+          <t>480390</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>28,65%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>34,13%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>439558</t>
+          <t>439496</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>489334</t>
+          <t>492336</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>66,79%</t>
+          <t>66,78%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>74,35%</t>
+          <t>74,81%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>472160</t>
+          <t>470858</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>527137</t>
+          <t>525480</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>63,02%</t>
+          <t>62,85%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>70,36%</t>
+          <t>70,14%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>928302</t>
+          <t>926988</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1005669</t>
+          <t>1004203</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>65,96%</t>
+          <t>65,87%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>71,46%</t>
+          <t>71,35%</t>
         </is>
       </c>
     </row>
